--- a/Excel-Finance/Finance-01/JLoka-Finance-01.xlsx
+++ b/Excel-Finance/Finance-01/JLoka-Finance-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\books-and-tutorials\Finance-Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel-Finance\Finance-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE392C9-C952-4B12-A4E2-98725B56AB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358D0F7E-FE9A-4EA3-9CA1-6FE9BF7400B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -632,7 +632,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -670,39 +670,9 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="2"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -728,91 +698,11 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="2"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="2"/>
-      </right>
-      <top style="thin">
-        <color theme="2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="2"/>
-      </right>
-      <top style="thin">
-        <color theme="2"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -1055,7 +945,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1082,58 +972,46 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="9"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1182,20 +1060,23 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1207,10 +1088,7 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1219,7 +1097,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1228,6 +1106,14 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1898,31 +1784,31 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.5363855935193429</c:v>
+                  <c:v>0.22518088577689821</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.43277185434202714</c:v>
+                  <c:v>4.6615126018486275E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.53656486979682871</c:v>
+                  <c:v>0.8702354955083681</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99046252507207722</c:v>
+                  <c:v>3.0926012166387684E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.92358806158591555</c:v>
+                  <c:v>8.8551138159630782E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.9907180350742735E-2</c:v>
+                  <c:v>0.65332271221650706</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.68232320326318707</c:v>
+                  <c:v>0.79215614449270955</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.46406046088502551</c:v>
+                  <c:v>0.26667953215936857</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.39904737830589421</c:v>
+                  <c:v>0.99577635299164857</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2062,31 +1948,31 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.72257606015225984</c:v>
+                  <c:v>0.22356504089203866</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.16951504839351839</c:v>
+                  <c:v>0.91547741076720424</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.15063242102889529</c:v>
+                  <c:v>1.5247083874135092E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.0815440580974016E-2</c:v>
+                  <c:v>0.57932526750454472</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1941542967680121</c:v>
+                  <c:v>0.22884202106672469</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.35363471401800151</c:v>
+                  <c:v>7.4932411321734005E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.16545561820313426</c:v>
+                  <c:v>0.15459971516135507</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.0706466903302299E-2</c:v>
+                  <c:v>0.28533575202753148</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.35625755920176883</c:v>
+                  <c:v>5.9259036510320717E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2226,31 +2112,31 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>2.2991435483274869E-2</c:v>
+                  <c:v>0.55144837190485618</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.88003983466223834</c:v>
+                  <c:v>0.26848087893021488</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.16331410868170881</c:v>
+                  <c:v>0.22986145590904394</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.47786551166393965</c:v>
+                  <c:v>0.2486301162043244</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.33562204986671973</c:v>
+                  <c:v>0.84990396601828477</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.22164654230503367</c:v>
+                  <c:v>3.5123198633126851E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.70531649021093235</c:v>
+                  <c:v>9.3087121970948261E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.39864848684549958</c:v>
+                  <c:v>0.37420685227850292</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.31746941730092082</c:v>
+                  <c:v>0.96217109063538808</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4041,7 +3927,7 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4119,7 +4005,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -4301,13 +4187,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{385DC015-9960-47FA-A637-6B66C3CB4FFA}" name="JLoka_Investors" displayName="JLoka_Investors" ref="B1:F9" totalsRowShown="0" dataDxfId="34" tableBorderDxfId="33">
-  <autoFilter ref="B1:F9" xr:uid="{22AB70FF-96FA-4025-A517-8BDE3ECE5EBF}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Jafar Loka-01"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:F9" xr:uid="{22AB70FF-96FA-4025-A517-8BDE3ECE5EBF}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{0BE1A407-37E2-45E1-A4B9-6EE27C852CA8}" name="INVESTOR_ID" dataDxfId="32"/>
     <tableColumn id="2" xr3:uid="{F40E02B0-B4B8-4130-A683-00045FEF2BC6}" name="INVESTOR_NAME" dataDxfId="31"/>
@@ -4698,14 +4578,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:D8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -4716,7 +4596,7 @@
         <v>46144</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -4727,7 +4607,7 @@
         <v>46145</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -4738,7 +4618,7 @@
         <v>46146</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -4749,7 +4629,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -4760,7 +4640,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -4771,7 +4651,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -4791,162 +4671,162 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A9EEF3-DE7A-4CAA-BA1C-C8A88C9A4643}">
   <dimension ref="B2:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="17.140625" customWidth="1"/>
+    <col min="2" max="4" width="17.109375" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="67" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="57" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="67" t="s">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="67">
+      <c r="C3" s="57">
         <v>720</v>
       </c>
-      <c r="D3" s="69">
+      <c r="D3" s="59">
         <v>20000</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="57" t="s">
         <v>98</v>
       </c>
       <c r="F3" t="str">
         <f>IF(Table5[[#This Row],[Credit Score]]&gt;700, "Yes", "No")</f>
         <v>Yes</v>
       </c>
-      <c r="G3" s="67" t="str">
+      <c r="G3" s="57" t="str">
         <f>IF(OR(Table5[[#This Row],[Good Credit?]]="Yes", Table5[[#This Row],[Employement Status]]="Full-Time"), "Approved", IF(AND(C3&gt;650, Table5[[#This Row],[Loan Amount]]&lt;12000), "Approved", "Denied"))</f>
         <v>Approved</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="67" t="s">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="67">
+      <c r="C4" s="57">
         <v>680</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="59">
         <v>15000</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="57" t="s">
         <v>99</v>
       </c>
       <c r="F4" t="str">
         <f>IF(Table5[[#This Row],[Credit Score]]&gt;700, "Yes", "No")</f>
         <v>No</v>
       </c>
-      <c r="G4" s="67" t="str">
+      <c r="G4" s="57" t="str">
         <f>IF(OR(Table5[[#This Row],[Good Credit?]]="Yes", Table5[[#This Row],[Employement Status]]="Full-Time"), "Approved", IF(AND(C4&gt;650, Table5[[#This Row],[Loan Amount]]&lt;12000), "Approved", "Denied"))</f>
         <v>Denied</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="67" t="s">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="67">
+      <c r="C5" s="57">
         <v>750</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="59">
         <v>25000</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="57" t="s">
         <v>98</v>
       </c>
       <c r="F5" t="str">
         <f>IF(Table5[[#This Row],[Credit Score]]&gt;700, "Yes", "No")</f>
         <v>Yes</v>
       </c>
-      <c r="G5" s="67" t="str">
+      <c r="G5" s="57" t="str">
         <f>IF(OR(Table5[[#This Row],[Good Credit?]]="Yes", Table5[[#This Row],[Employement Status]]="Full-Time"), "Approved", IF(AND(C5&gt;650, Table5[[#This Row],[Loan Amount]]&lt;12000), "Approved", "Denied"))</f>
         <v>Approved</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="67" t="s">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="67">
+      <c r="C6" s="57">
         <v>640</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="59">
         <v>10000</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="57" t="s">
         <v>100</v>
       </c>
       <c r="F6" t="str">
         <f>IF(Table5[[#This Row],[Credit Score]]&gt;700, "Yes", "No")</f>
         <v>No</v>
       </c>
-      <c r="G6" s="67" t="str">
+      <c r="G6" s="57" t="str">
         <f>IF(OR(Table5[[#This Row],[Good Credit?]]="Yes", Table5[[#This Row],[Employement Status]]="Full-Time"), "Approved", IF(AND(C6&gt;650, Table5[[#This Row],[Loan Amount]]&lt;12000), "Approved", "Denied"))</f>
         <v>Denied</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="67" t="s">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="67">
+      <c r="C7" s="57">
         <v>660</v>
       </c>
-      <c r="D7" s="69">
+      <c r="D7" s="59">
         <v>10000</v>
       </c>
-      <c r="E7" s="67" t="s">
+      <c r="E7" s="57" t="s">
         <v>99</v>
       </c>
       <c r="F7" t="str">
         <f>IF(Table5[[#This Row],[Credit Score]]&gt;700, "Yes", "No")</f>
         <v>No</v>
       </c>
-      <c r="G7" s="67" t="str">
+      <c r="G7" s="57" t="str">
         <f>IF(OR(Table5[[#This Row],[Good Credit?]]="Yes", Table5[[#This Row],[Employement Status]]="Full-Time"), "Approved", IF(AND(C7&gt;650, Table5[[#This Row],[Loan Amount]]&lt;12000), "Approved", "Denied"))</f>
         <v>Approved</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="67" t="s">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="67">
+      <c r="C8" s="57">
         <v>710</v>
       </c>
-      <c r="D8" s="69">
+      <c r="D8" s="59">
         <v>18000</v>
       </c>
-      <c r="E8" s="67" t="s">
+      <c r="E8" s="57" t="s">
         <v>99</v>
       </c>
       <c r="F8" t="str">
         <f>IF(Table5[[#This Row],[Credit Score]]&gt;700, "Yes", "No")</f>
         <v>Yes</v>
       </c>
-      <c r="G8" s="67" t="str">
+      <c r="G8" s="57" t="str">
         <f>IF(OR(Table5[[#This Row],[Good Credit?]]="Yes", Table5[[#This Row],[Employement Status]]="Full-Time"), "Approved", IF(AND(C8&gt;650, Table5[[#This Row],[Loan Amount]]&lt;12000), "Approved", "Denied"))</f>
         <v>Approved</v>
       </c>
@@ -4978,41 +4858,41 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{227D486A-352E-4CA0-80E8-EAB3033E6718}">
   <dimension ref="B2:I12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.88671875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="67" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="57" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>77</v>
       </c>
@@ -5021,25 +4901,25 @@
       </c>
       <c r="D3" s="2">
         <f ca="1">RANDBETWEEN(250, 3200)</f>
-        <v>1065</v>
-      </c>
-      <c r="E3" s="70">
+        <v>3198</v>
+      </c>
+      <c r="E3" s="60">
         <f ca="1">RANDBETWEEN(0, 2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>77</v>
       </c>
       <c r="H3" s="2">
         <f ca="1">VLOOKUP($G3, Table1[], 3, FALSE)</f>
-        <v>1065</v>
+        <v>3198</v>
       </c>
       <c r="I3" s="2">
         <f ca="1">VLOOKUP($G3, Table1[], 4, FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>78</v>
       </c>
@@ -5048,25 +4928,25 @@
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D12" ca="1" si="0">RANDBETWEEN(250, 3200)</f>
-        <v>1679</v>
-      </c>
-      <c r="E4" s="70">
+        <v>2902</v>
+      </c>
+      <c r="E4" s="60">
         <f t="shared" ref="E4:E12" ca="1" si="1">RANDBETWEEN(0, 2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="s">
         <v>78</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">VLOOKUP($G4, Table1[], 3, FALSE)</f>
-        <v>1679</v>
+        <v>2902</v>
       </c>
       <c r="I4" s="2">
         <f ca="1">VLOOKUP($G4, Table1[], 4, FALSE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>77</v>
       </c>
@@ -5075,132 +4955,132 @@
       </c>
       <c r="D5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1975</v>
-      </c>
-      <c r="E5" s="70">
+        <v>2829</v>
+      </c>
+      <c r="E5" s="60">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="2">
+        <f ca="1">VLOOKUP($G5, Table1[], 3, FALSE)</f>
+        <v>1855</v>
+      </c>
+      <c r="I5" s="2">
+        <f ca="1">VLOOKUP($G5, Table1[], 4, FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>1333</v>
+      </c>
+      <c r="E6" s="60">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="2">
+        <f ca="1">VLOOKUP($G6, Table1[], 3, FALSE)</f>
+        <v>2607</v>
+      </c>
+      <c r="I6" s="2">
+        <f ca="1">VLOOKUP($G6, Table1[], 4, FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>2553</v>
+      </c>
+      <c r="E7" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="G5" t="s">
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>79</v>
       </c>
-      <c r="H5" s="2">
-        <f ca="1">VLOOKUP($G5, Table1[], 3, FALSE)</f>
-        <v>2134</v>
-      </c>
-      <c r="I5" s="2">
-        <f ca="1">VLOOKUP($G5, Table1[], 4, FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1619</v>
-      </c>
-      <c r="E6" s="70">
+        <v>1855</v>
+      </c>
+      <c r="E8" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="2">
-        <f ca="1">VLOOKUP($G6, Table1[], 3, FALSE)</f>
-        <v>1363</v>
-      </c>
-      <c r="I6" s="2">
-        <f ca="1">VLOOKUP($G6, Table1[], 4, FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>77</v>
       </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1111</v>
-      </c>
-      <c r="E7" s="70">
+        <v>1231</v>
+      </c>
+      <c r="E9" s="60">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>560</v>
+      </c>
+      <c r="E10" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="2">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2134</v>
-      </c>
-      <c r="E8" s="70">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>1638</v>
-      </c>
-      <c r="E9" s="70">
+        <v>2607</v>
+      </c>
+      <c r="E11" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>2335</v>
-      </c>
-      <c r="E10" s="70">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>1363</v>
-      </c>
-      <c r="E11" s="70">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>79</v>
       </c>
@@ -5209,9 +5089,9 @@
       </c>
       <c r="D12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3074</v>
-      </c>
-      <c r="E12" s="70">
+        <v>855</v>
+      </c>
+      <c r="E12" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -5229,41 +5109,41 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12846ECA-6E1C-4031-BB27-C674131C97A8}">
   <dimension ref="B2:I12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.88671875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="67" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="67" t="s">
+      <c r="E2" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="57" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>77</v>
       </c>
@@ -5272,9 +5152,9 @@
       </c>
       <c r="D3" s="2">
         <f ca="1">RANDBETWEEN(250, 3200)</f>
-        <v>1708</v>
-      </c>
-      <c r="E3" s="70">
+        <v>2901</v>
+      </c>
+      <c r="E3" s="60">
         <f ca="1">RANDBETWEEN(0, 2)</f>
         <v>1</v>
       </c>
@@ -5283,14 +5163,14 @@
       </c>
       <c r="H3" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>1708</v>
+        <v>2901</v>
       </c>
       <c r="I3" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>78</v>
       </c>
@@ -5299,25 +5179,25 @@
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D12" ca="1" si="0">RANDBETWEEN(250, 3200)</f>
-        <v>2162</v>
-      </c>
-      <c r="E4" s="70">
+        <v>1365</v>
+      </c>
+      <c r="E4" s="60">
         <f t="shared" ref="E4:E12" ca="1" si="1">RANDBETWEEN(0, 2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="s">
         <v>78</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>2162</v>
+        <v>1365</v>
       </c>
       <c r="I4" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>77</v>
       </c>
@@ -5326,25 +5206,25 @@
       </c>
       <c r="D5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1912</v>
-      </c>
-      <c r="E5" s="70">
+        <v>1103</v>
+      </c>
+      <c r="E5" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
         <v>79</v>
       </c>
       <c r="H5" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>1473</v>
+        <v>2542</v>
       </c>
       <c r="I5" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>78</v>
       </c>
@@ -5353,9 +5233,9 @@
       </c>
       <c r="D6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2282</v>
-      </c>
-      <c r="E6" s="70">
+        <v>1537</v>
+      </c>
+      <c r="E6" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
@@ -5364,14 +5244,14 @@
       </c>
       <c r="H6" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>452</v>
+        <v>1787</v>
       </c>
       <c r="I6" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>77</v>
       </c>
@@ -5380,14 +5260,14 @@
       </c>
       <c r="D7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2495</v>
-      </c>
-      <c r="E7" s="70">
+        <v>1589</v>
+      </c>
+      <c r="E7" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>79</v>
       </c>
@@ -5396,14 +5276,14 @@
       </c>
       <c r="D8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1473</v>
-      </c>
-      <c r="E8" s="70">
+        <v>2542</v>
+      </c>
+      <c r="E8" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>77</v>
       </c>
@@ -5412,46 +5292,46 @@
       </c>
       <c r="D9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2138</v>
-      </c>
-      <c r="E9" s="70">
+        <v>838</v>
+      </c>
+      <c r="E9" s="60">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" ca="1" si="0"/>
+        <v>459</v>
+      </c>
+      <c r="E10" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="2">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1576</v>
-      </c>
-      <c r="E10" s="70">
+        <v>1787</v>
+      </c>
+      <c r="E11" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="2">
-        <f t="shared" ca="1" si="0"/>
-        <v>452</v>
-      </c>
-      <c r="E11" s="70">
-        <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>79</v>
       </c>
@@ -5460,9 +5340,9 @@
       </c>
       <c r="D12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3040</v>
-      </c>
-      <c r="E12" s="70">
+        <v>1472</v>
+      </c>
+      <c r="E12" s="60">
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
@@ -5479,274 +5359,274 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC1371C-14AF-4334-8E19-C4A01FA044F1}">
   <dimension ref="B2:M8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="13" max="13" width="26.140625" customWidth="1"/>
+    <col min="3" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" customWidth="1"/>
+    <col min="13" max="13" width="26.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="73" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="73" t="s">
+      <c r="G2" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="I2" s="74" t="s">
+      <c r="I2" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="74" t="s">
+      <c r="J2" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="L2" s="74" t="s">
+      <c r="L2" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="M2" s="74" t="s">
+      <c r="M2" s="64" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="75">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="65">
         <v>46045</v>
       </c>
-      <c r="C3" s="72">
+      <c r="C3" s="62">
         <f ca="1">RANDBETWEEN(120, 150)</f>
-        <v>148</v>
-      </c>
-      <c r="D3" s="72">
+        <v>139</v>
+      </c>
+      <c r="D3" s="62">
         <f ca="1">RANDBETWEEN(210, 260)</f>
-        <v>256</v>
-      </c>
-      <c r="E3" s="72">
+        <v>213</v>
+      </c>
+      <c r="E3" s="62">
         <f ca="1">RANDBETWEEN(330, 380)</f>
-        <v>360</v>
-      </c>
-      <c r="F3" s="72">
+        <v>371</v>
+      </c>
+      <c r="F3" s="62">
         <v>1250</v>
       </c>
-      <c r="G3" s="72">
+      <c r="G3" s="62">
         <v>2350</v>
       </c>
-      <c r="I3" s="75">
+      <c r="I3" s="65">
         <v>46076</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="K3" s="71">
+      <c r="K3" s="61">
         <f>MATCH(I3, $B$3:$B$8,0)</f>
         <v>2</v>
       </c>
-      <c r="L3" s="71">
+      <c r="L3" s="61">
         <f>MATCH(J3,$C$2:$G$2,0)</f>
         <v>3</v>
       </c>
-      <c r="M3" s="72" cm="1">
+      <c r="M3" s="62" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">INDEX($C$3:$G$8, K3,L3)</f>
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="75">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="65">
         <v>46076</v>
       </c>
-      <c r="C4" s="72">
+      <c r="C4" s="62">
         <f t="shared" ref="C4:C8" ca="1" si="0">RANDBETWEEN(120, 150)</f>
-        <v>124</v>
-      </c>
-      <c r="D4" s="72">
+        <v>130</v>
+      </c>
+      <c r="D4" s="62">
         <f t="shared" ref="D4:D8" ca="1" si="1">RANDBETWEEN(210, 260)</f>
-        <v>218</v>
-      </c>
-      <c r="E4" s="72">
+        <v>227</v>
+      </c>
+      <c r="E4" s="62">
         <f t="shared" ref="E4:E8" ca="1" si="2">RANDBETWEEN(330, 380)</f>
-        <v>363</v>
-      </c>
-      <c r="F4" s="72">
+        <v>349</v>
+      </c>
+      <c r="F4" s="62">
         <v>1300</v>
       </c>
-      <c r="G4" s="72">
+      <c r="G4" s="62">
         <v>2400</v>
       </c>
-      <c r="I4" s="75">
+      <c r="I4" s="65">
         <v>46076</v>
       </c>
-      <c r="J4" s="71" t="s">
+      <c r="J4" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="K4" s="71">
+      <c r="K4" s="61">
         <f t="shared" ref="K4:K7" si="3">MATCH(I4, $B$3:$B$8,0)</f>
         <v>2</v>
       </c>
-      <c r="L4" s="71">
+      <c r="L4" s="61">
         <f t="shared" ref="L4:L7" si="4">MATCH(J4,$C$2:$G$2,0)</f>
         <v>2</v>
       </c>
-      <c r="M4" s="72" cm="1">
+      <c r="M4" s="62" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">INDEX($C$3:$G$8, K4,L4)</f>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="75">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="65">
         <v>46104</v>
       </c>
-      <c r="C5" s="72">
+      <c r="C5" s="62">
+        <f t="shared" ca="1" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="D5" s="62">
+        <f t="shared" ca="1" si="1"/>
+        <v>226</v>
+      </c>
+      <c r="E5" s="62">
+        <f t="shared" ca="1" si="2"/>
+        <v>331</v>
+      </c>
+      <c r="F5" s="62">
+        <v>1350</v>
+      </c>
+      <c r="G5" s="62">
+        <v>2450</v>
+      </c>
+      <c r="I5" s="65">
+        <v>46104</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="61">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="L5" s="61">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="M5" s="62" cm="1">
+        <f t="array" ref="M5">INDEX($C$3:$G$8, K5,L5)</f>
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="65">
+        <v>46135</v>
+      </c>
+      <c r="C6" s="62">
         <f t="shared" ca="1" si="0"/>
         <v>146</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D6" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>232</v>
-      </c>
-      <c r="E5" s="72">
+        <v>246</v>
+      </c>
+      <c r="E6" s="62">
         <f t="shared" ca="1" si="2"/>
-        <v>349</v>
-      </c>
-      <c r="F5" s="72">
-        <v>1350</v>
-      </c>
-      <c r="G5" s="72">
-        <v>2450</v>
-      </c>
-      <c r="I5" s="75">
-        <v>46104</v>
-      </c>
-      <c r="J5" s="71" t="s">
+        <v>367</v>
+      </c>
+      <c r="F6" s="62">
+        <v>1400</v>
+      </c>
+      <c r="G6" s="62">
+        <v>2500</v>
+      </c>
+      <c r="I6" s="65">
+        <v>46135</v>
+      </c>
+      <c r="J6" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="K5" s="71">
+      <c r="K6" s="61">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="L5" s="71">
+        <v>4</v>
+      </c>
+      <c r="L6" s="61">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="M5" s="72" cm="1">
-        <f t="array" ref="M5">INDEX($C$3:$G$8, K5,L5)</f>
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="75">
-        <v>46135</v>
-      </c>
-      <c r="C6" s="72">
-        <f t="shared" ca="1" si="0"/>
-        <v>141</v>
-      </c>
-      <c r="D6" s="72">
-        <f t="shared" ca="1" si="1"/>
-        <v>254</v>
-      </c>
-      <c r="E6" s="72">
-        <f t="shared" ca="1" si="2"/>
-        <v>368</v>
-      </c>
-      <c r="F6" s="72">
-        <v>1400</v>
-      </c>
-      <c r="G6" s="72">
-        <v>2500</v>
-      </c>
-      <c r="I6" s="75">
-        <v>46135</v>
-      </c>
-      <c r="J6" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="K6" s="71">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="L6" s="71">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="M6" s="72" cm="1">
+      <c r="M6" s="62" cm="1">
         <f t="array" ref="M6">INDEX($C$3:$G$8, K6,L6)</f>
         <v>1400</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="75">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="65">
         <v>46165</v>
       </c>
-      <c r="C7" s="72">
+      <c r="C7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>146</v>
-      </c>
-      <c r="D7" s="72">
+        <v>125</v>
+      </c>
+      <c r="D7" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>215</v>
-      </c>
-      <c r="E7" s="72">
+        <v>260</v>
+      </c>
+      <c r="E7" s="62">
         <f t="shared" ca="1" si="2"/>
-        <v>345</v>
-      </c>
-      <c r="F7" s="72">
+        <v>330</v>
+      </c>
+      <c r="F7" s="62">
         <v>1450</v>
       </c>
-      <c r="G7" s="72">
+      <c r="G7" s="62">
         <v>2550</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="65">
         <v>46196</v>
       </c>
-      <c r="J7" s="71" t="s">
+      <c r="J7" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="61">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="61">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="M7" s="72" cm="1">
+      <c r="M7" s="62" cm="1">
         <f t="array" ref="M7">INDEX($C$3:$G$8, K7,L7)</f>
         <v>2600</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="75">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="65">
         <v>46196</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>134</v>
-      </c>
-      <c r="D8" s="72">
+        <v>142</v>
+      </c>
+      <c r="D8" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>215</v>
-      </c>
-      <c r="E8" s="72">
+        <v>220</v>
+      </c>
+      <c r="E8" s="62">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
-      </c>
-      <c r="F8" s="72">
+        <v>332</v>
+      </c>
+      <c r="F8" s="62">
         <v>1500</v>
       </c>
-      <c r="G8" s="72">
+      <c r="G8" s="62">
         <v>2600</v>
       </c>
     </row>
@@ -5758,224 +5638,224 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FAAC275-79FD-4ECC-93CD-B834A0A54184}">
   <dimension ref="B2:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="76" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="68" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="32" t="s">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C3">
         <f ca="1">RANDBETWEEN(5, 50)</f>
-        <v>35</v>
-      </c>
-      <c r="D3" s="79">
+        <v>44</v>
+      </c>
+      <c r="D3" s="69">
         <f ca="1">RANDBETWEEN(1000, 100000)</f>
-        <v>36846</v>
-      </c>
-      <c r="E3" s="85" cm="1">
+        <v>77720</v>
+      </c>
+      <c r="E3" s="75" cm="1">
         <f t="array" aca="1" ref="E3:E13" ca="1">C3:C13*D3:D13</f>
-        <v>1289610</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="32" t="s">
+        <v>3419680</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C13" ca="1" si="0">RANDBETWEEN(5, 50)</f>
-        <v>16</v>
-      </c>
-      <c r="D4" s="79">
+        <v>28</v>
+      </c>
+      <c r="D4" s="69">
         <f t="shared" ref="D4:D13" ca="1" si="1">RANDBETWEEN(1000, 100000)</f>
-        <v>40271</v>
-      </c>
-      <c r="E4" s="86">
+        <v>49865</v>
+      </c>
+      <c r="E4" s="76">
         <f ca="1"/>
-        <v>644336</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="32" t="s">
+        <v>1396220</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="23" t="s">
         <v>17</v>
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="D5" s="79">
+        <v>47</v>
+      </c>
+      <c r="D5" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>47225</v>
-      </c>
-      <c r="E5" s="86">
+        <v>18741</v>
+      </c>
+      <c r="E5" s="76">
         <f ca="1"/>
-        <v>1605650</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="32" t="s">
+        <v>880827</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="D6" s="79">
+        <v>11</v>
+      </c>
+      <c r="D6" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>74261</v>
-      </c>
-      <c r="E6" s="86">
+        <v>86323</v>
+      </c>
+      <c r="E6" s="76">
         <f ca="1"/>
-        <v>2821918</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="32" t="s">
+        <v>949553</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="23" t="s">
         <v>129</v>
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="D7" s="79">
+        <v>15</v>
+      </c>
+      <c r="D7" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>34040</v>
-      </c>
-      <c r="E7" s="86">
+        <v>97775</v>
+      </c>
+      <c r="E7" s="76">
         <f ca="1"/>
-        <v>1259480</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="32" t="s">
+        <v>1466625</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="23" t="s">
         <v>130</v>
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="D8" s="79">
+        <v>18</v>
+      </c>
+      <c r="D8" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>36301</v>
-      </c>
-      <c r="E8" s="86">
+        <v>6004</v>
+      </c>
+      <c r="E8" s="76">
         <f ca="1"/>
-        <v>871224</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="32" t="s">
+        <v>108072</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="23" t="s">
         <v>131</v>
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="D9" s="79">
+        <v>49</v>
+      </c>
+      <c r="D9" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>7802</v>
-      </c>
-      <c r="E9" s="86">
+        <v>87532</v>
+      </c>
+      <c r="E9" s="76">
         <f ca="1"/>
-        <v>366694</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="32" t="s">
+        <v>4289068</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="23" t="s">
         <v>132</v>
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="D10" s="79">
+        <v>47</v>
+      </c>
+      <c r="D10" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>15790</v>
-      </c>
-      <c r="E10" s="86">
+        <v>65568</v>
+      </c>
+      <c r="E10" s="76">
         <f ca="1"/>
-        <v>315800</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="32" t="s">
+        <v>3081696</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="23" t="s">
         <v>133</v>
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="D11" s="79">
+        <v>36</v>
+      </c>
+      <c r="D11" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>52436</v>
-      </c>
-      <c r="E11" s="86">
+        <v>88406</v>
+      </c>
+      <c r="E11" s="76">
         <f ca="1"/>
-        <v>524360</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="32" t="s">
+        <v>3182616</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="23" t="s">
         <v>134</v>
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="D12" s="79">
+        <v>28</v>
+      </c>
+      <c r="D12" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>86368</v>
-      </c>
-      <c r="E12" s="86">
+        <v>82861</v>
+      </c>
+      <c r="E12" s="76">
         <f ca="1"/>
-        <v>1381888</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="80" t="s">
+        <v>2320108</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="D13" s="82">
+        <v>19</v>
+      </c>
+      <c r="D13" s="72">
         <f t="shared" ca="1" si="1"/>
-        <v>15930</v>
-      </c>
-      <c r="E13" s="87">
+        <v>71798</v>
+      </c>
+      <c r="E13" s="77">
         <f ca="1"/>
-        <v>430110</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="83" t="s">
+        <v>1364162</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="73" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="88">
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="78">
         <f ca="1">SUM(_xlfn.ANCHORARRAY(E3))</f>
-        <v>11511070</v>
+        <v>22458627</v>
       </c>
     </row>
   </sheetData>
@@ -5987,15 +5867,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0303D7-B63C-4C14-ADB0-194A7F9BABAD}">
   <dimension ref="B2:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
@@ -6009,7 +5889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
@@ -6023,7 +5903,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
@@ -6037,7 +5917,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
@@ -6051,7 +5931,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
@@ -6073,250 +5953,265 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDF221F-0025-402B-A438-3CAAFA8F5C9B}">
   <dimension ref="A1:N11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="21.42578125" customWidth="1"/>
-    <col min="14" max="14" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+    <col min="14" max="14" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="89" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89" t="s">
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89" t="s">
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="90">
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="81">
         <v>46144</v>
       </c>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="92">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83">
         <v>250.25</v>
       </c>
-      <c r="F3" s="92"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="91"/>
-      <c r="J3" s="91"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
       <c r="N3" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="90">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="81">
         <v>46145</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="92">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="83">
         <v>300</v>
       </c>
-      <c r="F4" s="92"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="93">
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="79">
         <f>(E4-E3)/E3</f>
         <v>0.19880119880119881</v>
       </c>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
       <c r="N4" s="10">
         <f>AVERAGE(I4:L11)</f>
         <v>-8.1596436336491718E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="90">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="81">
         <v>46146</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="92">
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="83">
         <v>350.15</v>
       </c>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="93">
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="79">
         <f>(E5-E4)/E4</f>
         <v>0.1671666666666666</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="90">
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="81">
         <v>46147</v>
       </c>
-      <c r="B6" s="91"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="92">
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="83">
         <v>650.5</v>
       </c>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="93">
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="79">
         <f>(E6-E5)/E5</f>
         <v>0.85777523918320731</v>
       </c>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
       <c r="N6" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="81">
         <v>46148</v>
       </c>
-      <c r="B7" s="91"/>
-      <c r="C7" s="91"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="92">
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="83">
         <v>600.35</v>
       </c>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="93">
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="79">
         <f t="shared" ref="I7:I10" si="0">(E7-E6)/E6</f>
         <v>-7.7094542659492657E-2</v>
       </c>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
       <c r="N7" s="12" t="str">
         <f>IF(N4&gt;0,"Positive","Negative")</f>
         <v>Negative</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="90">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="81">
         <v>46149</v>
       </c>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="92">
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="83">
         <v>150.19999999999999</v>
       </c>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="93">
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="79">
         <f t="shared" si="0"/>
         <v>-0.74981260931123517</v>
       </c>
-      <c r="J8" s="93"/>
-      <c r="K8" s="93"/>
-      <c r="L8" s="93"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="90">
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="81">
         <v>46150</v>
       </c>
-      <c r="B9" s="91"/>
-      <c r="C9" s="91"/>
-      <c r="D9" s="91"/>
-      <c r="E9" s="92">
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="83">
         <v>55.5</v>
       </c>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="93">
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="79">
         <f t="shared" si="0"/>
         <v>-0.6304926764314247</v>
       </c>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="90">
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="79"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="81">
         <v>46151</v>
       </c>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91"/>
-      <c r="D10" s="91"/>
-      <c r="E10" s="92">
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="83">
         <v>80.5</v>
       </c>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="93">
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="79">
         <f t="shared" si="0"/>
         <v>0.45045045045045046</v>
       </c>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="90">
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="81">
         <v>46152</v>
       </c>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="92">
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="83">
         <v>10.5</v>
       </c>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="93">
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="79">
         <f t="shared" ref="I11" si="1">(E11-E10)/E10</f>
         <v>-0.86956521739130432</v>
       </c>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
     <mergeCell ref="I10:L10"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A11:D11"/>
@@ -6333,21 +6228,6 @@
     <mergeCell ref="I9:L9"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6356,15 +6236,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5081B24-AD91-4661-91C0-87FEDD27A3C2}">
   <dimension ref="B2:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="3" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="13" t="s">
         <v>20</v>
       </c>
@@ -6388,7 +6268,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="14">
         <v>46144</v>
       </c>
@@ -6417,7 +6297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="14">
         <v>46145</v>
       </c>
@@ -6430,7 +6310,7 @@
       <c r="H4" s="17"/>
       <c r="I4" s="17"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="14">
         <v>46146</v>
       </c>
@@ -6444,7 +6324,7 @@
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="14">
         <v>46147</v>
       </c>
@@ -6458,7 +6338,7 @@
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="14">
         <v>46148</v>
       </c>
@@ -6472,7 +6352,7 @@
       <c r="H7" s="17"/>
       <c r="I7" s="17"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="14">
         <v>46149</v>
       </c>
@@ -6486,7 +6366,7 @@
       <c r="H8" s="17"/>
       <c r="I8" s="17"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="14">
         <v>46150</v>
       </c>
@@ -6500,7 +6380,7 @@
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="14">
         <v>46151</v>
       </c>
@@ -6514,7 +6394,7 @@
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="14">
         <v>46152</v>
       </c>
@@ -6528,7 +6408,7 @@
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="14">
         <v>46153</v>
       </c>
@@ -6542,7 +6422,7 @@
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="14">
         <v>46154</v>
       </c>
@@ -6556,7 +6436,7 @@
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="14">
         <v>46155</v>
       </c>
@@ -6570,7 +6450,7 @@
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="14">
         <v>46156</v>
       </c>
@@ -6584,7 +6464,7 @@
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="14">
         <v>46157</v>
       </c>
@@ -6598,7 +6478,7 @@
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="14">
         <v>46158</v>
       </c>
@@ -6620,35 +6500,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D44A967B-77A0-46E6-9D75-84A934B0FAA8}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="95" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96" t="s">
+      <c r="D1" s="86"/>
+      <c r="E1" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="96"/>
-      <c r="G1" s="95" t="s">
+      <c r="F1" s="86"/>
+      <c r="G1" s="85" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="95"/>
-      <c r="B2" s="95"/>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
       <c r="C2" s="21" t="s">
         <v>33</v>
       </c>
@@ -6661,169 +6541,169 @@
       <c r="F2" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="95"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="G2" s="85"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="93">
         <f ca="1">RANDBETWEEN(10, 50)</f>
-        <v>43</v>
-      </c>
-      <c r="C3" s="30">
+        <v>13</v>
+      </c>
+      <c r="C3" s="12">
         <f ca="1">RANDBETWEEN(2, 10)</f>
-        <v>9</v>
-      </c>
-      <c r="D3" s="22">
+        <v>4</v>
+      </c>
+      <c r="D3" s="12">
         <f ca="1">RANDBETWEEN(2, 10)</f>
+        <v>7</v>
+      </c>
+      <c r="E3" s="22">
+        <f ca="1">$B3*C3</f>
+        <v>52</v>
+      </c>
+      <c r="F3" s="25">
+        <f ca="1">$B3*D3</f>
+        <v>91</v>
+      </c>
+      <c r="G3" s="28">
+        <f ca="1">(E3+F3)/(E$8+F$8)</f>
+        <v>0.13763233878729547</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="93">
+        <f t="shared" ref="B4:B7" ca="1" si="0">RANDBETWEEN(10, 50)</f>
+        <v>27</v>
+      </c>
+      <c r="C4" s="12">
+        <f t="shared" ref="C4:D7" ca="1" si="1">RANDBETWEEN(2, 10)</f>
         <v>3</v>
       </c>
-      <c r="E3" s="29">
-        <f ca="1">$B3*C3</f>
-        <v>387</v>
-      </c>
-      <c r="F3" s="35">
-        <f ca="1">$B3*D3</f>
-        <v>129</v>
-      </c>
-      <c r="G3" s="38">
-        <f ca="1">(E3+F3)/(E$8+F$8)</f>
-        <v>0.25146198830409355</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="24">
-        <f t="shared" ref="B4:B7" ca="1" si="0">RANDBETWEEN(10, 50)</f>
-        <v>20</v>
-      </c>
-      <c r="C4" s="31">
-        <f t="shared" ref="C4:D7" ca="1" si="1">RANDBETWEEN(2, 10)</f>
-        <v>10</v>
-      </c>
-      <c r="D4" s="25">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="E4" s="29">
-        <f t="shared" ref="E4:F7" ca="1" si="2">$B4*C4</f>
-        <v>200</v>
-      </c>
-      <c r="F4" s="36">
-        <f t="shared" ca="1" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="G4" s="38">
-        <f ca="1">(E4+F4)/(E$8+F$8)</f>
-        <v>0.12670565302144249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="24">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C5" s="31">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="D5" s="28">
-        <f t="shared" ca="1" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="E5" s="29">
-        <f t="shared" ca="1" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="F5" s="35">
-        <f t="shared" ca="1" si="2"/>
-        <v>320</v>
-      </c>
-      <c r="G5" s="38">
-        <f t="shared" ref="G5:G7" ca="1" si="3">(E5+F5)/(E$8+F$8)</f>
-        <v>0.21442495126705652</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="24">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C6" s="26">
+      <c r="D4" s="12">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="D6" s="25">
-        <f t="shared" ca="1" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="E6" s="29">
+      <c r="E4" s="22">
+        <f t="shared" ref="E4:F7" ca="1" si="2">$B4*C4</f>
+        <v>81</v>
+      </c>
+      <c r="F4" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>68</v>
-      </c>
-      <c r="F6" s="35">
-        <f t="shared" ca="1" si="2"/>
-        <v>306</v>
-      </c>
-      <c r="G6" s="38">
-        <f t="shared" ca="1" si="3"/>
-        <v>0.18226120857699804</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="33">
+        <v>54</v>
+      </c>
+      <c r="G4" s="28">
+        <f ca="1">(E4+F4)/(E$8+F$8)</f>
+        <v>0.12993262752646775</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C7" s="32">
-        <f t="shared" ca="1" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="D7" s="27">
+        <v>22</v>
+      </c>
+      <c r="C5" s="12">
         <f t="shared" ca="1" si="1"/>
         <v>6</v>
       </c>
-      <c r="E7" s="29">
+      <c r="D5" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E5" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>264</v>
-      </c>
-      <c r="F7" s="35">
+        <v>132</v>
+      </c>
+      <c r="F5" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>198</v>
-      </c>
-      <c r="G7" s="38">
+        <v>110</v>
+      </c>
+      <c r="G5" s="28">
+        <f t="shared" ref="G5:G7" ca="1" si="3">(E5+F5)/(E$8+F$8)</f>
+        <v>0.23291626564003851</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="92" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="93">
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C6" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E6" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>164</v>
+      </c>
+      <c r="F6" s="25">
+        <f t="shared" ca="1" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="G6" s="28">
         <f t="shared" ca="1" si="3"/>
-        <v>0.22514619883040934</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+        <v>0.23676612127045235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="93">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C7" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E7" s="22">
+        <f t="shared" ca="1" si="2"/>
+        <v>147</v>
+      </c>
+      <c r="F7" s="25">
+        <f t="shared" ca="1" si="2"/>
+        <v>126</v>
+      </c>
+      <c r="G7" s="28">
+        <f t="shared" ca="1" si="3"/>
+        <v>0.26275264677574589</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="37">
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="27">
         <f ca="1">SUM(E3:E7)</f>
-        <v>1039</v>
-      </c>
-      <c r="F8" s="37">
+        <v>576</v>
+      </c>
+      <c r="F8" s="27">
         <f ca="1">SUM(F3:F7)</f>
-        <v>1013</v>
-      </c>
-      <c r="G8" s="34"/>
+        <v>463</v>
+      </c>
+      <c r="G8" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6840,225 +6720,225 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A353DF0-38D4-4363-880C-1DE1AFCD6401}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="97" t="s">
+      <c r="F1" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="97"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="G1" s="87"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="31">
         <f ca="1">RANDBETWEEN(500, 1000)</f>
-        <v>804</v>
-      </c>
-      <c r="F2" s="45" t="s">
+        <v>761</v>
+      </c>
+      <c r="F2" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="46">
+      <c r="G2" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F2, $C$2:$C$9)</f>
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="44">
+      <c r="C3" s="34">
         <f t="shared" ref="C3:C9" ca="1" si="0">RANDBETWEEN(500, 1000)</f>
-        <v>895</v>
-      </c>
-      <c r="F3" s="34" t="s">
+        <v>738</v>
+      </c>
+      <c r="F3" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F2, $B$2:$B$9, F3)</f>
-        <v>731</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="44">
+      <c r="C4" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>844</v>
-      </c>
-      <c r="F4" s="34" t="s">
+        <v>869</v>
+      </c>
+      <c r="F4" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="34">
+      <c r="G4" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F2, $B$2:$B$9, F4)</f>
-        <v>997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>518</v>
-      </c>
-      <c r="F5" s="45" t="s">
+        <v>795</v>
+      </c>
+      <c r="F5" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F5, $C$2:$C$9)</f>
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>731</v>
-      </c>
-      <c r="F6" s="34" t="s">
+        <v>853</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F5, $B$2:$B$9, F6)</f>
-        <v>804</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>997</v>
-      </c>
-      <c r="F7" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="F7" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F5, $B$2:$B$9, F7)</f>
-        <v>895</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="52" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>802</v>
-      </c>
-      <c r="F8" s="45" t="s">
+        <v>885</v>
+      </c>
+      <c r="F8" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F8, $C$2:$C$9)</f>
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>619</v>
-      </c>
-      <c r="F9" s="34" t="s">
+        <v>598</v>
+      </c>
+      <c r="F9" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F8, $B$2:$B$9, F9)</f>
-        <v>844</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F10" s="34" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F8, $B$2:$B$9, F10)</f>
-        <v>518</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F11" s="45" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F11" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="46">
+      <c r="G11" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F11, $C$2:$C$9)</f>
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F12" s="34" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F12" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F11, $B$2:$B$9, F12)</f>
-        <v>802</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F13" s="34" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F13" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F11, $B$2:$B$9, F13)</f>
-        <v>619</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F14" s="40" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="33">
         <f ca="1">SUM(G2,G5,G8,G11)</f>
-        <v>6210</v>
+        <v>6009</v>
       </c>
     </row>
   </sheetData>
@@ -7072,182 +6952,182 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22AB70FF-96FA-4025-A517-8BDE3ECE5EBF}">
   <dimension ref="B1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" style="55" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="55" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="55" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" style="55" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="55" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" style="45" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="45" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" style="45" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" style="45" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" style="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B1" s="56" t="s">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="49" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="60" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="61">
+      <c r="E2" s="51">
         <v>60000</v>
       </c>
-      <c r="F2" s="62">
+      <c r="F2" s="52">
         <f>DATE(2026, 10, 5)</f>
         <v>46300</v>
       </c>
     </row>
-    <row r="3" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="60" t="s">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="61">
+      <c r="E3" s="51">
         <v>50000</v>
       </c>
-      <c r="F3" s="62">
+      <c r="F3" s="52">
         <f>DATE(2026, 4, 7)</f>
         <v>46119</v>
       </c>
     </row>
-    <row r="4" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="60" t="s">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="51">
         <v>25000</v>
       </c>
-      <c r="F4" s="62">
+      <c r="F4" s="52">
         <f>DATE(2026, 8, 7)</f>
         <v>46241</v>
       </c>
     </row>
-    <row r="5" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="60" t="s">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="51">
         <v>15000</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="52">
         <f>DATE(2026, 5, 8)</f>
         <v>46150</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="60" t="s">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="51">
         <v>10000</v>
       </c>
-      <c r="F6" s="62">
+      <c r="F6" s="52">
         <f>DATE(2026, 9, 7)</f>
         <v>46272</v>
       </c>
     </row>
-    <row r="7" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="60" t="s">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="51">
         <v>7500</v>
       </c>
-      <c r="F7" s="62">
+      <c r="F7" s="52">
         <f>DATE(2026, 5, 7)</f>
         <v>46149</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="60" t="s">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="51">
         <v>7000</v>
       </c>
-      <c r="F8" s="62">
+      <c r="F8" s="52">
         <f>DATE(2026, 5, 7)</f>
         <v>46149</v>
       </c>
     </row>
-    <row r="9" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="63" t="s">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="64">
+      <c r="E9" s="54">
         <v>6000</v>
       </c>
-      <c r="F9" s="65">
+      <c r="F9" s="55">
         <f>DATE(2026, 6, 6)</f>
         <v>46179</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C12" s="98" t="s">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C12" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="66">
+      <c r="D12" s="88"/>
+      <c r="E12" s="56">
         <f>SUM(JLoka_Investors[INVESTMENT AMOUNT (USD)])</f>
         <v>180500</v>
       </c>
@@ -7278,220 +7158,220 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3323-DAD4-4089-9A46-7712A3CF5F64}">
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="99" t="s">
+    <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="B2" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="67"/>
-    </row>
-    <row r="3" spans="2:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67" t="s">
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="57"/>
+    </row>
+    <row r="3" spans="2:6" s="57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="57" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="57" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2011</v>
       </c>
       <c r="C4" s="3">
         <f ca="1">RAND()</f>
-        <v>0.68950921678621457</v>
+        <v>0.11080121388456066</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" ref="D4:E4" ca="1" si="0">RAND()</f>
-        <v>0.56595269121806013</v>
+        <v>0.88566478997338571</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.47548086004728651</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.97117624755734233</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2012</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" ref="C5:E14" ca="1" si="1">RAND()</f>
-        <v>5.749831692446028E-3</v>
+        <v>0.53966467512723337</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.57885741536574653</v>
+        <v>0.73072885920293484</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>7.724548887117777E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.87907102792245906</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2013</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.5363855935193429</v>
+        <v>0.22518088577689821</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.72257606015225984</v>
+        <v>0.22356504089203866</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>2.2991435483274869E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.55144837190485618</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2014</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.43277185434202714</v>
+        <v>4.6615126018486275E-2</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.16951504839351839</v>
+        <v>0.91547741076720424</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.88003983466223834</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.26848087893021488</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>2015</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.53656486979682871</v>
+        <v>0.8702354955083681</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.15063242102889529</v>
+        <v>1.5247083874135092E-2</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.16331410868170881</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.22986145590904394</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>2016</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99046252507207722</v>
+        <v>3.0926012166387684E-2</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>9.0815440580974016E-2</v>
+        <v>0.57932526750454472</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.47786551166393965</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.2486301162043244</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>2017</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.92358806158591555</v>
+        <v>8.8551138159630782E-2</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.1941542967680121</v>
+        <v>0.22884202106672469</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.33562204986671973</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.84990396601828477</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2018</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>7.9907180350742735E-2</v>
+        <v>0.65332271221650706</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.35363471401800151</v>
+        <v>7.4932411321734005E-2</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22164654230503367</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+        <v>3.5123198633126851E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2019</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.68232320326318707</v>
+        <v>0.79215614449270955</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.16545561820313426</v>
+        <v>0.15459971516135507</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.70531649021093235</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+        <v>9.3087121970948261E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>2020</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.46406046088502551</v>
+        <v>0.26667953215936857</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>8.0706466903302299E-2</v>
+        <v>0.28533575202753148</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39864848684549958</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+        <v>0.37420685227850292</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>2021</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.39904737830589421</v>
+        <v>0.99577635299164857</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.35625755920176883</v>
+        <v>5.9259036510320717E-3</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.31746941730092082</v>
+        <v>0.96217109063538808</v>
       </c>
     </row>
   </sheetData>
@@ -7509,13 +7389,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8721280-4213-4B53-9A0B-5F17D269CBD8}">
   <dimension ref="B2:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>80</v>
       </c>
@@ -7523,35 +7403,35 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="68">
+      <c r="C3" s="58">
         <v>0.60699999999999998</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="68">
+      <c r="C4" s="58">
         <v>0.29299999999999998</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="68">
+      <c r="C5" s="58">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="68">
+      <c r="C6" s="58">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
